--- a/artfynd/A 16874-2026 artfynd.xlsx
+++ b/artfynd/A 16874-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132397226</v>
+        <v>132544811</v>
       </c>
       <c r="B2" t="n">
-        <v>92355</v>
+        <v>92647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Prästeskogen, Prästeskogen, Sm</t>
+          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587984</v>
+        <v>588083</v>
       </c>
       <c r="R2" t="n">
-        <v>6313100</v>
+        <v>6312985</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132395320</v>
+        <v>132394401</v>
       </c>
       <c r="B3" t="n">
-        <v>96715</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -821,14 +812,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
+          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588084</v>
+        <v>587978</v>
       </c>
       <c r="R3" t="n">
-        <v>6313148</v>
+        <v>6313220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132396034</v>
+        <v>132394909</v>
       </c>
       <c r="B4" t="n">
-        <v>96715</v>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,14 +918,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
+          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587996</v>
+        <v>588084</v>
       </c>
       <c r="R4" t="n">
-        <v>6313057</v>
+        <v>6313148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,38 +984,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132395569</v>
+        <v>132395781</v>
       </c>
       <c r="B5" t="n">
-        <v>57954</v>
+        <v>96783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1095,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132394401</v>
+        <v>132396034</v>
       </c>
       <c r="B6" t="n">
-        <v>96715</v>
+        <v>96783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,7 +1120,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1139,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587978</v>
+        <v>587996</v>
       </c>
       <c r="R6" t="n">
-        <v>6313220</v>
+        <v>6313057</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132396728</v>
+        <v>132544935</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,34 +1207,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587996</v>
+        <v>588093</v>
       </c>
       <c r="R7" t="n">
-        <v>6313057</v>
+        <v>6312987</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,57 +1298,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132396639</v>
+        <v>132547541</v>
       </c>
       <c r="B8" t="n">
-        <v>58118</v>
+        <v>96783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587996</v>
+        <v>588013</v>
       </c>
       <c r="R8" t="n">
-        <v>6313057</v>
+        <v>6313139</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1372,12 +1363,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132395781</v>
+        <v>132723151</v>
       </c>
       <c r="B9" t="n">
-        <v>96715</v>
+        <v>96783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,17 +1435,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
+          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588055</v>
+        <v>588083</v>
       </c>
       <c r="R9" t="n">
-        <v>6313093</v>
+        <v>6313146</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,12 +1469,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,53 +1501,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132395145</v>
+        <v>132397226</v>
       </c>
       <c r="B10" t="n">
-        <v>57954</v>
+        <v>92385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
+          <t>Prästeskogen, Prästeskogen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588084</v>
+        <v>587984</v>
       </c>
       <c r="R10" t="n">
-        <v>6313148</v>
+        <v>6313100</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1612,53 +1607,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132546678</v>
+        <v>132722974</v>
       </c>
       <c r="B11" t="n">
-        <v>58119</v>
+        <v>92385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Prästeskogen, Prästeskogen, Sm</t>
+          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588013</v>
+        <v>588076</v>
       </c>
       <c r="R11" t="n">
-        <v>6313139</v>
+        <v>6313188</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1682,12 +1672,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132544935</v>
+        <v>132395145</v>
       </c>
       <c r="B12" t="n">
-        <v>96718</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1725,42 +1715,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
+          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588093</v>
+        <v>588084</v>
       </c>
       <c r="R12" t="n">
-        <v>6312987</v>
+        <v>6313148</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,12 +1774,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,38 +1806,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132545067</v>
+        <v>132395569</v>
       </c>
       <c r="B13" t="n">
-        <v>58119</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1856,13 +1846,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588093</v>
+        <v>588055</v>
       </c>
       <c r="R13" t="n">
-        <v>6312987</v>
+        <v>6313093</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1886,12 +1876,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132547541</v>
+        <v>132547998</v>
       </c>
       <c r="B14" t="n">
-        <v>96718</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,24 +1919,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
@@ -1959,7 +1954,7 @@
         <v>6313139</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2015,14 +2010,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132547998</v>
+        <v>132722331</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2046,22 +2041,22 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
+          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588013</v>
+        <v>587899</v>
       </c>
       <c r="R15" t="n">
-        <v>6313139</v>
+        <v>6313224</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2085,12 +2080,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132544811</v>
+        <v>132722667</v>
       </c>
       <c r="B16" t="n">
-        <v>92573</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,34 +2123,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588083</v>
+        <v>587932</v>
       </c>
       <c r="R16" t="n">
-        <v>6312985</v>
+        <v>6313284</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132722667</v>
+        <v>132396639</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>58136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,27 +2225,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2254,13 +2258,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587932</v>
+        <v>587996</v>
       </c>
       <c r="R17" t="n">
-        <v>6313284</v>
+        <v>6313057</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2284,12 +2288,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,57 +2320,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723151</v>
+        <v>132545067</v>
       </c>
       <c r="B18" t="n">
-        <v>96718</v>
+        <v>58136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
+          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588083</v>
+        <v>588093</v>
       </c>
       <c r="R18" t="n">
-        <v>6313146</v>
+        <v>6312987</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2422,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132722331</v>
+        <v>132546678</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,42 +2433,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strömsrum 1:2, Strömsrum 1:2, Sm</t>
+          <t>Prästeskogen, Prästeskogen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587899</v>
+        <v>588013</v>
       </c>
       <c r="R19" t="n">
-        <v>6313224</v>
+        <v>6313139</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,6 +2521,205 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132544927</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>588093</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6312987</v>
+      </c>
+      <c r="S20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132396728</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ingemåla 5:2, ingemåla 5:2, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>587996</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6313057</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16874-2026 artfynd.xlsx
+++ b/artfynd/A 16874-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132544811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132394401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132394909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132395781</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396034</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132544935</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132547541</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132723151</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397226</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132722974</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132395145</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132395569</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132547998</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2109,6 +2179,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132722331</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2211,6 +2286,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132722667</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2317,6 +2397,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396639</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132545067</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2521,6 +2611,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132546678</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132544927</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2720,8 +2820,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>